--- a/Result/profitability/1722.xlsx
+++ b/Result/profitability/1722.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.98</v>
       </c>
       <c r="M2" t="n">
-        <v>0.41625</v>
+        <v>0.3525</v>
       </c>
       <c r="N2" t="n">
-        <v>13.17375</v>
+        <v>13.9275</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.93</v>
       </c>
       <c r="M3" t="n">
-        <v>0.43875</v>
+        <v>0.41125</v>
       </c>
       <c r="N3" t="n">
-        <v>12.3825</v>
+        <v>13.21</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.48</v>
       </c>
       <c r="M4" t="n">
-        <v>0.44125</v>
+        <v>0.45875</v>
       </c>
       <c r="N4" t="n">
-        <v>11.90125</v>
+        <v>13.76875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.41</v>
+        <v>0.385</v>
       </c>
       <c r="N5" t="n">
-        <v>9.880000000000001</v>
+        <v>10.47875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>0.40625</v>
+        <v>0.365</v>
       </c>
       <c r="N6" t="n">
-        <v>9.422500000000001</v>
+        <v>10.43</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5062500000000001</v>
+        <v>0.55625</v>
       </c>
       <c r="N7" t="n">
-        <v>10.83875</v>
+        <v>11.665</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.98</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4037500000000001</v>
+        <v>0.41</v>
       </c>
       <c r="N8" t="n">
-        <v>11.38</v>
+        <v>13.245</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2343</v>
+      </c>
+      <c r="E75" t="n">
+        <v>658</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="G75" t="n">
+        <v>372</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-83</v>
+      </c>
+      <c r="J75" t="n">
+        <v>290</v>
+      </c>
+      <c r="K75" t="n">
+        <v>234</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.16375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.04999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.263157894736842</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>2.13447782546495</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4545454545454546</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.789999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2797897196261681</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
